--- a/data/trans_dic/IP19C01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Clase-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que en su última visita al dentista fue por revisión o chequeo</t>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,2; 85,4</t>
+          <t>65,83; 84,89</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,66; 82,58</t>
+          <t>60,55; 81,48</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,27; 85,19</t>
+          <t>61,47; 85,92</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>65,9; 84,27</t>
+          <t>66,1; 84,34</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,96; 87,16</t>
+          <t>67,94; 87,14</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,24; 86,59</t>
+          <t>66,01; 87,0</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>55,76; 77,39</t>
+          <t>56,43; 77,25</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78,3; 91,4</t>
+          <t>78,38; 91,54</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>69,37; 83,78</t>
+          <t>70,37; 84,13</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,74; 81,86</t>
+          <t>66,55; 81,93</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>61,89; 78,33</t>
+          <t>63,19; 78,78</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>76,1; 87,1</t>
+          <t>75,77; 86,78</t>
         </is>
       </c>
     </row>
@@ -856,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,06; 79,64</t>
+          <t>52,05; 77,43</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,59; 83,11</t>
+          <t>62,14; 83,9</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,87; 88,12</t>
+          <t>70,13; 89,02</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,52; 90,36</t>
+          <t>73,94; 90,19</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>51,8; 77,84</t>
+          <t>53,66; 78,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,28; 84,6</t>
+          <t>62,33; 83,93</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>67,94; 86,13</t>
+          <t>66,68; 85,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>78,97; 93,16</t>
+          <t>79,38; 93,53</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>56,77; 75,19</t>
+          <t>58,77; 75,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,67; 81,47</t>
+          <t>66,99; 80,98</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,24; 85,28</t>
+          <t>71,87; 85,0</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,54; 90,09</t>
+          <t>79,87; 90,73</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,44; 79,66</t>
+          <t>53,37; 78,79</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>66,95; 86,73</t>
+          <t>65,68; 86,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,27; 88,05</t>
+          <t>64,3; 88,04</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>60,87; 87,64</t>
+          <t>57,78; 86,72</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,02; 80,98</t>
+          <t>62,78; 81,7</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>61,54; 83,6</t>
+          <t>60,17; 83,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,12; 91,35</t>
+          <t>70,59; 92,49</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>51,83; 80,25</t>
+          <t>53,08; 81,4</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>61,73; 76,94</t>
+          <t>62,39; 77,91</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,61; 82,65</t>
+          <t>66,99; 82,2</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>71,92; 87,74</t>
+          <t>72,65; 87,61</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,87; 80,84</t>
+          <t>59,9; 81,42</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,59; 78,99</t>
+          <t>64,73; 79,12</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,75; 79,17</t>
+          <t>64,05; 79,18</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,43; 76,96</t>
+          <t>63,45; 77,06</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,66; 90,37</t>
+          <t>77,93; 90,32</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,38; 79,83</t>
+          <t>66,15; 79,71</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,83; 83,56</t>
+          <t>69,68; 83,61</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,24; 82,48</t>
+          <t>68,63; 82,12</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,06; 81,9</t>
+          <t>65,95; 82,58</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,41; 77,98</t>
+          <t>66,96; 77,68</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68,72; 79,73</t>
+          <t>69,3; 79,65</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67,81; 77,75</t>
+          <t>67,98; 77,74</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,42; 84,56</t>
+          <t>74,04; 84,57</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,06; 66,55</t>
+          <t>44,07; 66,39</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>56,02; 73,52</t>
+          <t>55,93; 72,47</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,88; 72,24</t>
+          <t>53,7; 72,48</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>64,69; 87,55</t>
+          <t>65,96; 88,13</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,97; 76,99</t>
+          <t>58,87; 75,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>57,48; 74,71</t>
+          <t>56,31; 75,18</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,06; 86,25</t>
+          <t>70,56; 86,69</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,8; 93,89</t>
+          <t>77,44; 93,78</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>56,19; 69,53</t>
+          <t>55,24; 69,63</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,07; 72,05</t>
+          <t>59,09; 71,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,08; 77,46</t>
+          <t>65,01; 77,33</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>75,86; 89,19</t>
+          <t>76,17; 89,97</t>
         </is>
       </c>
     </row>
@@ -1416,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,74; 72,12</t>
+          <t>47,24; 71,87</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>65,48; 90,38</t>
+          <t>64,83; 89,8</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62,05; 87,14</t>
+          <t>61,42; 86,75</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74,04; 92,32</t>
+          <t>74,7; 92,71</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>66,77; 87,25</t>
+          <t>65,2; 87,23</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,08; 91,43</t>
+          <t>71,18; 91,44</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,74; 82,13</t>
+          <t>53,86; 82,46</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>74,01; 95,66</t>
+          <t>72,83; 95,48</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,79; 76,82</t>
+          <t>59,23; 75,92</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>72,86; 88,86</t>
+          <t>73,17; 88,55</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,97; 81,62</t>
+          <t>61,95; 80,88</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76,17; 91,78</t>
+          <t>77,72; 91,74</t>
         </is>
       </c>
     </row>
@@ -1556,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>63,2; 71,66</t>
+          <t>62,81; 71,47</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67,37; 75,51</t>
+          <t>67,48; 75,7</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,53; 76,38</t>
+          <t>68,79; 76,37</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77,14; 84,64</t>
+          <t>76,87; 84,67</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,66; 76,66</t>
+          <t>69,06; 76,25</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>70,7; 78,54</t>
+          <t>71,02; 78,74</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,69; 79,16</t>
+          <t>71,83; 79,15</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>78,63; 85,65</t>
+          <t>78,19; 85,51</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>67,44; 73,07</t>
+          <t>67,23; 72,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70,47; 76,01</t>
+          <t>70,69; 76,23</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71,72; 77,01</t>
+          <t>71,31; 76,81</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,36; 84,63</t>
+          <t>79,16; 84,25</t>
         </is>
       </c>
     </row>
@@ -1638,4 +1639,1622 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N25"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que en su última visita al dentista fue por revisión o chequeo (tasa de respuesta: 99,77%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>Grupo I y II</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>61</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>96</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>41697</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>35613</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>32512</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>54432</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>39013</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>31751</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>33778</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>82883</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>80709</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>67364</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>66289</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>137315</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>36070; 46513</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>29669; 39924</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>26444; 36963</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>47446; 60536</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>33535; 43010</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>26989; 35567</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>28505; 39024</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>75316; 87964</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>73289; 87627</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>59815; 73635</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>59103; 73687</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>127185; 145679</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>Grupo III</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>51</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>27235</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>35410</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>44946</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>52406</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>24817</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>39911</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>41987</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>62629</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>52053</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>75321</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>86933</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>115035</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>21080; 31356</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>29849; 40301</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>39087; 49616</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>46361; 56549</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>19878; 29254</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>33081; 44546</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>36029; 46270</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>56823; 66955</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>45572; 58577</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>67735; 81878</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>78886; 93295</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>107250; 121837</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>Grupo IV y V</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>93</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>91</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>76</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>23586</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>33083</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>24815</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>21166</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>38507</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>29548</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>29125</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>24681</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>62093</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>62631</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>53941</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>45847</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>18684; 27586</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>27888; 36838</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>20515; 28087</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>16137; 24219</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>33504; 43604</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>24314; 33694</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>24671; 32327</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>19245; 29516</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>55138; 68853</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>55513; 68117</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>48567; 58574</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>38452; 52261</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VI</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>94</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>213</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>201</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>223</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>249</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>70725</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>65722</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>78908</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>94676</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>70512</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>75739</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>80025</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>95160</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>141237</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>141462</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>158932</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>189836</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>63525; 77650</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>58430; 72233</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>70952; 86175</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>86536; 100298</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>63608; 76648</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>68258; 81911</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>72228; 86431</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>84018; 105198</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>130105; 150922</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>131116; 150686</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>147575; 168747</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>176530; 201647</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Grupo VII</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>30475</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>53150</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>44718</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>54236</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>47652</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>48940</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>58587</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>90486</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>78127</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>102090</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>103306</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>144722</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>24090; 36285</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>45994; 59591</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>37626; 50785</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>45182; 60370</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>41228; 53202</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>41483; 55380</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>52343; 64304</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>79916; 96781</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>68886; 86827</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>92111; 111798</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>93770; 111538</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>130775; 154472</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="1" t="inlineStr">
+        <is>
+          <t>No ha trabajado</t>
+        </is>
+      </c>
+      <c r="B19" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>35</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>52</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>98</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="1" t="n"/>
+      <c r="B20" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>23970</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>20305</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>24916</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>38130</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>27867</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>31341</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>22753</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>38081</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>51838</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>51647</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>47669</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>76211</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="1" t="n"/>
+      <c r="B21" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>18898; 28749</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>16655; 23069</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>20024; 28282</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>33515; 41594</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>23293; 31166</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>26704; 34305</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>17750; 27173</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
+          <t>32145; 42137</t>
+        </is>
+      </c>
+      <c r="K21" s="2" t="inlineStr">
+        <is>
+          <t>44855; 57495</t>
+        </is>
+      </c>
+      <c r="L21" s="2" t="inlineStr">
+        <is>
+          <t>46248; 55969</t>
+        </is>
+      </c>
+      <c r="M21" s="2" t="inlineStr">
+        <is>
+          <t>40609; 53020</t>
+        </is>
+      </c>
+      <c r="N21" s="2" t="inlineStr">
+        <is>
+          <t>69171; 81647</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B22" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>327</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>345</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>361</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>453</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="K22" s="2" t="inlineStr">
+        <is>
+          <t>702</t>
+        </is>
+      </c>
+      <c r="L22" s="2" t="inlineStr">
+        <is>
+          <t>713</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>728</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>919</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="1" t="n"/>
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>217689</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>243284</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>250816</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>315046</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>248367</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>257230</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>266253</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>393920</t>
+        </is>
+      </c>
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>466056</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>500514</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>517070</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>708966</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="1" t="n"/>
+      <c r="B24" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>202922; 230933</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>228502; 256341</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>237412; 263591</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>297347; 327523</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>235957; 260534</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>243955; 270474</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>252745; 278509</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>374287; 409297</t>
+        </is>
+      </c>
+      <c r="K24" s="2" t="inlineStr">
+        <is>
+          <t>446943; 484071</t>
+        </is>
+      </c>
+      <c r="L24" s="2" t="inlineStr">
+        <is>
+          <t>482226; 520024</t>
+        </is>
+      </c>
+      <c r="M24" s="2" t="inlineStr">
+        <is>
+          <t>497066; 535407</t>
+        </is>
+      </c>
+      <c r="N24" s="2" t="inlineStr">
+        <is>
+          <t>685091; 729148</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="11">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A22:A24"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP19C01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Clase-trans_dic.xlsx
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>65,83; 84,89</t>
+          <t>66,76; 85,09</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>60,55; 81,48</t>
+          <t>59,4; 82,62</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>61,47; 85,92</t>
+          <t>62,39; 85,61</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66,1; 84,34</t>
+          <t>66,34; 84,37</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>67,94; 87,14</t>
+          <t>68,03; 87,03</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,01; 87,0</t>
+          <t>66,93; 87,03</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>56,43; 77,25</t>
+          <t>54,8; 76,65</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>78,38; 91,54</t>
+          <t>79,3; 92,19</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70,37; 84,13</t>
+          <t>70,57; 83,74</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,55; 81,93</t>
+          <t>66,8; 81,95</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>63,19; 78,78</t>
+          <t>62,98; 78,25</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,77; 86,78</t>
+          <t>75,26; 86,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>52,05; 77,43</t>
+          <t>55,01; 80,16</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,14; 83,9</t>
+          <t>62,63; 84,06</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70,13; 89,02</t>
+          <t>71,58; 88,48</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,94; 90,19</t>
+          <t>73,69; 90,55</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>53,66; 78,97</t>
+          <t>52,44; 79,19</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>62,33; 83,93</t>
+          <t>64,85; 84,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>66,68; 85,64</t>
+          <t>68,1; 85,57</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,38; 93,53</t>
+          <t>79,9; 92,72</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,77; 75,54</t>
+          <t>58,42; 76,16</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,99; 80,98</t>
+          <t>66,64; 80,8</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>71,87; 85,0</t>
+          <t>72,75; 84,93</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,87; 90,73</t>
+          <t>79,47; 90,42</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,37; 78,79</t>
+          <t>53,63; 78,61</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,68; 86,76</t>
+          <t>65,95; 86,93</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,3; 88,04</t>
+          <t>64,87; 88,18</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>57,78; 86,72</t>
+          <t>59,36; 87,46</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,78; 81,7</t>
+          <t>62,37; 80,5</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,17; 83,39</t>
+          <t>60,21; 83,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>70,59; 92,49</t>
+          <t>71,39; 91,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,08; 81,4</t>
+          <t>53,13; 81,33</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,39; 77,91</t>
+          <t>62,15; 77,37</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66,99; 82,2</t>
+          <t>68,29; 83,16</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,65; 87,61</t>
+          <t>72,79; 87,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>59,9; 81,42</t>
+          <t>60,39; 80,8</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>64,73; 79,12</t>
+          <t>63,95; 78,77</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>64,05; 79,18</t>
+          <t>63,98; 79,13</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,45; 77,06</t>
+          <t>63,92; 77,59</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>77,93; 90,32</t>
+          <t>78,74; 90,39</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>66,15; 79,71</t>
+          <t>65,21; 79,97</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>69,68; 83,61</t>
+          <t>70,88; 83,9</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,63; 82,12</t>
+          <t>68,17; 82,5</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,95; 82,58</t>
+          <t>66,11; 82,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>66,96; 77,68</t>
+          <t>67,15; 77,36</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>69,3; 79,65</t>
+          <t>68,93; 79,52</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>67,98; 77,74</t>
+          <t>68,14; 77,43</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,04; 84,57</t>
+          <t>74,17; 84,21</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>44,07; 66,39</t>
+          <t>45,06; 66,38</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,93; 72,47</t>
+          <t>55,7; 73,2</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>53,7; 72,48</t>
+          <t>54,13; 73,15</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,96; 88,13</t>
+          <t>65,15; 88,02</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>58,87; 75,96</t>
+          <t>59,23; 76,78</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>56,31; 75,18</t>
+          <t>55,85; 74,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,56; 86,69</t>
+          <t>70,41; 86,51</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,44; 93,78</t>
+          <t>77,34; 93,57</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55,24; 69,63</t>
+          <t>55,1; 68,79</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>59,09; 71,71</t>
+          <t>58,94; 71,57</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>65,01; 77,33</t>
+          <t>64,46; 77,41</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,17; 89,97</t>
+          <t>76,55; 89,65</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,24; 71,87</t>
+          <t>47,5; 72,07</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,83; 89,8</t>
+          <t>64,63; 89,82</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>61,42; 86,75</t>
+          <t>62,6; 86,47</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>74,7; 92,71</t>
+          <t>73,01; 92,3</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>65,2; 87,23</t>
+          <t>64,74; 87,1</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>71,18; 91,44</t>
+          <t>72,12; 91,57</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>53,86; 82,46</t>
+          <t>54,64; 81,82</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>72,83; 95,48</t>
+          <t>73,13; 93,98</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,23; 75,92</t>
+          <t>59,03; 76,1</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73,17; 88,55</t>
+          <t>73,03; 88,78</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>61,95; 80,88</t>
+          <t>62,72; 80,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>77,72; 91,74</t>
+          <t>76,72; 91,38</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,81; 71,47</t>
+          <t>62,74; 71,73</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67,48; 75,7</t>
+          <t>67,43; 75,4</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,79; 76,37</t>
+          <t>68,37; 76,11</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>76,87; 84,67</t>
+          <t>77,36; 84,81</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>69,06; 76,25</t>
+          <t>68,71; 76,83</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,02; 78,74</t>
+          <t>71,02; 78,67</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>71,83; 79,15</t>
+          <t>72,02; 79,48</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>78,19; 85,51</t>
+          <t>78,71; 85,66</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>67,23; 72,82</t>
+          <t>67,36; 72,82</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70,69; 76,23</t>
+          <t>70,32; 76,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71,31; 76,81</t>
+          <t>71,29; 77,07</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,16; 84,25</t>
+          <t>79,29; 84,33</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36070; 46513</t>
+          <t>36583; 46628</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29669; 39924</t>
+          <t>29104; 40483</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26444; 36963</t>
+          <t>26839; 36830</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47446; 60536</t>
+          <t>47617; 60556</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33535; 43010</t>
+          <t>33580; 42954</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26989; 35567</t>
+          <t>27365; 35583</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>28505; 39024</t>
+          <t>27680; 38719</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>75316; 87964</t>
+          <t>76199; 88589</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73289; 87627</t>
+          <t>73504; 87216</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>59815; 73635</t>
+          <t>60041; 73655</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59103; 73687</t>
+          <t>58909; 73190</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>127185; 145679</t>
+          <t>126336; 145187</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21080; 31356</t>
+          <t>22278; 32465</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>29849; 40301</t>
+          <t>30084; 40377</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39087; 49616</t>
+          <t>39892; 49316</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46361; 56549</t>
+          <t>46206; 56773</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19878; 29254</t>
+          <t>19426; 29337</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>33081; 44546</t>
+          <t>34420; 44755</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36029; 46270</t>
+          <t>36794; 46231</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>56823; 66955</t>
+          <t>57196; 66376</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45572; 58577</t>
+          <t>45300; 59058</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67735; 81878</t>
+          <t>67375; 81698</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>78886; 93295</t>
+          <t>79849; 93218</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>107250; 121837</t>
+          <t>106720; 121419</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18684; 27586</t>
+          <t>18775; 27523</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>27888; 36838</t>
+          <t>28001; 36911</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20515; 28087</t>
+          <t>20696; 28131</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16137; 24219</t>
+          <t>16577; 24426</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33504; 43604</t>
+          <t>33286; 42963</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24314; 33694</t>
+          <t>24331; 33657</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24671; 32327</t>
+          <t>24952; 32031</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19245; 29516</t>
+          <t>19263; 29489</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>55138; 68853</t>
+          <t>54928; 68383</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>55513; 68117</t>
+          <t>56595; 68915</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48567; 58574</t>
+          <t>48663; 58562</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38452; 52261</t>
+          <t>38762; 51865</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>63525; 77650</t>
+          <t>62755; 77300</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58430; 72233</t>
+          <t>58371; 72190</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>70952; 86175</t>
+          <t>71478; 86767</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>86536; 100298</t>
+          <t>87440; 100374</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>63608; 76648</t>
+          <t>62698; 76895</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>68258; 81911</t>
+          <t>69442; 82198</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>72228; 86431</t>
+          <t>71747; 86831</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84018; 105198</t>
+          <t>84225; 105431</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130105; 150922</t>
+          <t>130466; 150306</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>131116; 150686</t>
+          <t>130404; 150442</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>147575; 168747</t>
+          <t>147906; 168078</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>176530; 201647</t>
+          <t>176846; 200789</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24090; 36285</t>
+          <t>24628; 36282</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45994; 59591</t>
+          <t>45804; 60193</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37626; 50785</t>
+          <t>37924; 51256</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>45182; 60370</t>
+          <t>44627; 60291</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41228; 53202</t>
+          <t>41480; 53769</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41483; 55380</t>
+          <t>41140; 54900</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52343; 64304</t>
+          <t>52227; 64171</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79916; 96781</t>
+          <t>79812; 96565</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68886; 86827</t>
+          <t>68711; 85773</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>92111; 111798</t>
+          <t>91880; 111581</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>93770; 111538</t>
+          <t>92979; 111654</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>130775; 154472</t>
+          <t>131442; 153934</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>18898; 28749</t>
+          <t>19001; 28827</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16655; 23069</t>
+          <t>16603; 23075</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20024; 28282</t>
+          <t>20409; 28189</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>33515; 41594</t>
+          <t>32757; 41409</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23293; 31166</t>
+          <t>23128; 31117</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>26704; 34305</t>
+          <t>27058; 34353</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>17750; 27173</t>
+          <t>18005; 26962</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32145; 42137</t>
+          <t>32273; 41476</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44855; 57495</t>
+          <t>44703; 57631</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46248; 55969</t>
+          <t>46159; 56118</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>40609; 53020</t>
+          <t>41113; 52849</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>69171; 81647</t>
+          <t>68276; 81329</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>202922; 230933</t>
+          <t>202719; 231756</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228502; 256341</t>
+          <t>228337; 255335</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>237412; 263591</t>
+          <t>235980; 262704</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>297347; 327523</t>
+          <t>299245; 328047</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>235957; 260534</t>
+          <t>234759; 262521</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>243955; 270474</t>
+          <t>243964; 270248</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>252745; 278509</t>
+          <t>253404; 279682</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>374287; 409297</t>
+          <t>376745; 410032</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>446943; 484071</t>
+          <t>447790; 484070</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>482226; 520024</t>
+          <t>479693; 518529</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>497066; 535407</t>
+          <t>496942; 537207</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>685091; 729148</t>
+          <t>686202; 729860</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP19C01-Clase-trans_dic.xlsx
+++ b/data/trans_dic/IP19C01-Clase-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -649,42 +649,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>79,04%</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>77,66%</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>66,87%</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>85,63%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>76,1%</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>72,69%</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>75,58%</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>75,84%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>79,04%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>77,66%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>66,87%</t>
-        </is>
-      </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>74,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,87%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>66,76; 85,09</t>
+          <t>68,96; 87,16</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>59,4; 82,62</t>
+          <t>66,24; 86,59</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>62,39; 85,61</t>
+          <t>55,76; 77,39</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>66,34; 84,37</t>
+          <t>77,49; 91,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>68,03; 87,03</t>
+          <t>65,2; 85,4</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>66,93; 87,03</t>
+          <t>60,66; 82,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>54,8; 76,65</t>
+          <t>62,27; 85,19</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>79,3; 92,19</t>
+          <t>65,26; 83,49</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>70,57; 83,74</t>
+          <t>69,37; 83,78</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>66,8; 81,95</t>
+          <t>66,74; 81,86</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>62,98; 78,25</t>
+          <t>61,89; 78,33</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>75,26; 86,49</t>
+          <t>74,77; 86,22</t>
         </is>
       </c>
     </row>
@@ -789,42 +789,42 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>66,99%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>75,2%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>77,71%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>88,05%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>67,25%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>73,72%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>80,64%</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>83,58%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>66,99%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>75,2%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>77,71%</t>
-        </is>
-      </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>87,49%</t>
+          <t>83,63%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>85,66%</t>
+          <t>85,92%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>55,01; 80,16</t>
+          <t>51,8; 77,84</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>62,63; 84,06</t>
+          <t>64,28; 84,6</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>71,58; 88,48</t>
+          <t>67,94; 86,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>73,69; 90,55</t>
+          <t>79,9; 93,66</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>52,44; 79,19</t>
+          <t>55,06; 79,64</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>64,85; 84,33</t>
+          <t>62,59; 83,11</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>68,1; 85,57</t>
+          <t>70,87; 88,12</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>79,9; 92,72</t>
+          <t>73,82; 90,35</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>58,42; 76,16</t>
+          <t>56,77; 75,19</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66,64; 80,8</t>
+          <t>66,67; 81,47</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>72,75; 84,93</t>
+          <t>72,24; 85,28</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>79,47; 90,42</t>
+          <t>79,65; 90,28</t>
         </is>
       </c>
     </row>
@@ -929,42 +929,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>72,15%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>73,12%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>83,33%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>69,85%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>67,37%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>77,91%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>77,78%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>75,79%</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>72,15%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>73,12%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>83,33%</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>76,54%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,91%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>53,63; 78,61</t>
+          <t>62,02; 80,98</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>65,95; 86,93</t>
+          <t>61,54; 83,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>64,87; 88,18</t>
+          <t>70,12; 91,35</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>59,36; 87,46</t>
+          <t>53,75; 81,31</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>62,37; 80,5</t>
+          <t>53,44; 79,66</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>60,21; 83,29</t>
+          <t>66,95; 86,73</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>71,39; 91,65</t>
+          <t>64,27; 88,05</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53,13; 81,33</t>
+          <t>61,6; 88,27</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>62,15; 77,37</t>
+          <t>61,73; 76,94</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>68,29; 83,16</t>
+          <t>66,61; 82,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>72,79; 87,6</t>
+          <t>71,92; 87,74</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>60,39; 80,8</t>
+          <t>62,94; 82,1</t>
         </is>
       </c>
     </row>
@@ -1069,42 +1069,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>73,33%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>77,31%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>76,03%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>75,41%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>72,07%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>72,04%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>70,56%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>85,26%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>73,33%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>77,31%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>76,03%</t>
-        </is>
-      </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,7%</t>
+          <t>84,05%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,48%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>63,95; 78,77</t>
+          <t>65,38; 79,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>63,98; 79,13</t>
+          <t>69,83; 83,56</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>63,92; 77,59</t>
+          <t>68,24; 82,48</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>78,74; 90,39</t>
+          <t>66,15; 82,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>65,21; 79,97</t>
+          <t>64,59; 78,99</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>70,88; 83,9</t>
+          <t>63,75; 79,17</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>68,17; 82,5</t>
+          <t>63,43; 76,96</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>66,11; 82,76</t>
+          <t>76,61; 89,43</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>67,15; 77,36</t>
+          <t>67,41; 77,98</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>68,93; 79,52</t>
+          <t>68,72; 79,73</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>68,14; 77,43</t>
+          <t>67,81; 77,75</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>74,17; 84,21</t>
+          <t>74,49; 84,31</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>68,04%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>66,43%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>78,98%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>87,05%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>55,76%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>64,64%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>63,82%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>79,18%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>68,04%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>66,43%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>78,98%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>82,6%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>84,29%</t>
+          <t>85,17%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>45,06; 66,38</t>
+          <t>58,97; 76,99</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>55,7; 73,2</t>
+          <t>57,48; 74,71</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>54,13; 73,15</t>
+          <t>70,06; 86,25</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>65,15; 88,02</t>
+          <t>76,72; 93,54</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>59,23; 76,78</t>
+          <t>44,06; 66,55</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,85; 74,52</t>
+          <t>56,02; 73,52</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>70,41; 86,51</t>
+          <t>53,88; 72,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>77,34; 93,57</t>
+          <t>73,26; 90,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>55,1; 68,79</t>
+          <t>56,19; 69,53</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>58,94; 71,57</t>
+          <t>58,07; 72,05</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64,46; 77,41</t>
+          <t>65,08; 77,46</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>76,55; 89,65</t>
+          <t>78,75; 89,73</t>
         </is>
       </c>
     </row>
@@ -1349,42 +1349,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>78,0%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>83,54%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>69,05%</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>86,3%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>59,93%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>79,04%</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>76,43%</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>84,99%</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>78,0%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>83,54%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>69,05%</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>85,63%</t>
+          <t>85,75%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>47,5; 72,07</t>
+          <t>66,77; 87,25</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>64,63; 89,82</t>
+          <t>71,08; 91,43</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>62,6; 86,47</t>
+          <t>54,74; 82,13</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>73,01; 92,3</t>
+          <t>73,98; 95,48</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>64,74; 87,1</t>
+          <t>47,74; 72,12</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>72,12; 91,57</t>
+          <t>65,48; 90,38</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>54,64; 81,82</t>
+          <t>62,05; 87,14</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>73,13; 93,98</t>
+          <t>74,2; 92,55</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>59,03; 76,1</t>
+          <t>59,79; 76,82</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>73,03; 88,78</t>
+          <t>72,86; 88,86</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62,72; 80,62</t>
+          <t>62,97; 81,62</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>76,72; 91,38</t>
+          <t>76,34; 91,74</t>
         </is>
       </c>
     </row>
@@ -1489,42 +1489,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>72,69%</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>74,88%</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>75,67%</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>82,42%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>67,38%</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>71,84%</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>72,67%</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>81,45%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>72,69%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>74,88%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>75,67%</t>
-        </is>
-      </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>82,3%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,06%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>62,74; 71,73</t>
+          <t>68,66; 76,66</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>67,43; 75,4</t>
+          <t>70,7; 78,54</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>68,37; 76,11</t>
+          <t>71,69; 79,16</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77,36; 84,81</t>
+          <t>78,7; 85,64</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>68,71; 76,83</t>
+          <t>63,2; 71,66</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>71,02; 78,67</t>
+          <t>67,37; 75,51</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>72,02; 79,48</t>
+          <t>68,53; 76,38</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>78,71; 85,66</t>
+          <t>77,51; 84,57</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>67,36; 72,82</t>
+          <t>67,44; 73,07</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>70,32; 76,01</t>
+          <t>70,47; 76,01</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71,29; 77,07</t>
+          <t>71,72; 77,01</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>79,29; 84,33</t>
+          <t>79,46; 84,7</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1683,7 +1683,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1791,42 +1791,42 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>48</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>50</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>79</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>47</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>48</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>102</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1859,42 +1859,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>39013</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>31751</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>33778</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>77559</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
           <t>41697</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t>35613</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="I5" s="2" t="inlineStr">
         <is>
           <t>32512</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>54432</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>39013</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>31751</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>33778</t>
-        </is>
-      </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>82883</t>
+          <t>53521</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>137315</t>
+          <t>131081</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>36583; 46628</t>
+          <t>34037; 43020</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>29104; 40483</t>
+          <t>27083; 35402</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>26839; 36830</t>
+          <t>28168; 39091</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>47617; 60556</t>
+          <t>70183; 82661</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33580; 42954</t>
+          <t>35729; 46794</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>27365; 35583</t>
+          <t>29721; 40461</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>27680; 38719</t>
+          <t>26789; 36650</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>76199; 88589</t>
+          <t>46669; 59703</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>73504; 87216</t>
+          <t>72247; 87255</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>60041; 73655</t>
+          <t>59982; 73578</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58909; 73190</t>
+          <t>57888; 73269</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>126336; 145187</t>
+          <t>121186; 139751</t>
         </is>
       </c>
     </row>
@@ -1999,42 +1999,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>38</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>59</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
           <t>42</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>51</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="I7" s="2" t="inlineStr">
         <is>
           <t>63</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="J7" s="2" t="inlineStr">
         <is>
           <t>76</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>59</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
@@ -2067,42 +2067,42 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>24817</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>39911</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>41987</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>61995</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>27235</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>35410</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>44946</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>52406</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>24817</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>39911</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>41987</t>
-        </is>
-      </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>62629</t>
+          <t>54558</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>115035</t>
+          <t>116553</t>
         </is>
       </c>
     </row>
@@ -2135,62 +2135,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22278; 32465</t>
+          <t>19189; 28835</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>30084; 40377</t>
+          <t>34117; 44903</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>39892; 49316</t>
+          <t>36708; 46536</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46206; 56773</t>
+          <t>56254; 65942</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>19426; 29337</t>
+          <t>22300; 32253</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>34420; 44755</t>
+          <t>30064; 39918</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>36794; 46231</t>
+          <t>39497; 49112</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>57196; 66376</t>
+          <t>48157; 58944</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>45300; 59058</t>
+          <t>44024; 58309</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67375; 81698</t>
+          <t>67412; 82374</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>79849; 93218</t>
+          <t>79299; 93611</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>106720; 121419</t>
+          <t>108045; 122461</t>
         </is>
       </c>
     </row>
@@ -2207,42 +2207,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>58</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>43</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>32</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>35</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>48</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
         <is>
           <t>31</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>58</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>32</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -2275,42 +2275,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>38507</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>29548</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>29125</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>24092</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>23586</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>33083</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="I11" s="2" t="inlineStr">
         <is>
           <t>24815</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>21166</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>38507</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>29548</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>29125</t>
-        </is>
-      </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>24681</t>
+          <t>22206</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>45847</t>
+          <t>46299</t>
         </is>
       </c>
     </row>
@@ -2343,62 +2343,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>18775; 27523</t>
+          <t>33102; 43219</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>28001; 36911</t>
+          <t>24865; 33781</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>20696; 28131</t>
+          <t>24507; 31927</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16577; 24426</t>
+          <t>18539; 28043</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>33286; 42963</t>
+          <t>18708; 27888</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24331; 33657</t>
+          <t>28428; 36824</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>24952; 32031</t>
+          <t>20505; 28091</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19263; 29489</t>
+          <t>17872; 25607</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>54928; 68383</t>
+          <t>54553; 68000</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>56595; 68915</t>
+          <t>55200; 68487</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>48663; 58562</t>
+          <t>48085; 58655</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>38762; 51865</t>
+          <t>39967; 52134</t>
         </is>
       </c>
     </row>
@@ -2415,42 +2415,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>107</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>94</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="I13" s="2" t="inlineStr">
         <is>
           <t>114</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>137</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>106</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>109</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>112</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2483,42 +2483,42 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>70512</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>75739</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>80025</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>92256</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>70725</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>65722</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="I14" s="2" t="inlineStr">
         <is>
           <t>78908</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>94676</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>70512</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>75739</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>80025</t>
-        </is>
-      </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>95160</t>
+          <t>91628</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>189836</t>
+          <t>183884</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>62755; 77300</t>
+          <t>62870; 76760</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>58371; 72190</t>
+          <t>68406; 81862</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>71478; 86767</t>
+          <t>71820; 86811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>87440; 100374</t>
+          <t>80932; 101121</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>62698; 76895</t>
+          <t>63384; 77515</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>69442; 82198</t>
+          <t>58156; 72227</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>71747; 86831</t>
+          <t>70932; 86064</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>84225; 105431</t>
+          <t>83521; 97503</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>130466; 150306</t>
+          <t>130978; 151502</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>130404; 150442</t>
+          <t>130010; 150841</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>147906; 168078</t>
+          <t>147192; 168781</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>176846; 200789</t>
+          <t>172346; 195069</t>
         </is>
       </c>
     </row>
@@ -2623,42 +2623,42 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>72</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>69</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>74</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="I16" s="2" t="inlineStr">
         <is>
           <t>66</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
+      <c r="J16" s="2" t="inlineStr">
         <is>
           <t>78</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>72</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>69</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>95</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -2691,42 +2691,42 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>47652</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>48940</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>58587</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>81853</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>30475</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>53150</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="I17" s="2" t="inlineStr">
         <is>
           <t>44718</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>54236</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>47652</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>48940</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>58587</t>
-        </is>
-      </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>90486</t>
+          <t>57049</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>144722</t>
+          <t>138902</t>
         </is>
       </c>
     </row>
@@ -2759,62 +2759,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>24628; 36282</t>
+          <t>41298; 53922</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>45804; 60193</t>
+          <t>42341; 55037</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>37924; 51256</t>
+          <t>51972; 63977</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>44627; 60291</t>
+          <t>72134; 87951</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>41480; 53769</t>
+          <t>24081; 36373</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>41140; 54900</t>
+          <t>46068; 60453</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>52227; 64171</t>
+          <t>37754; 50614</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>79812; 96565</t>
+          <t>50601; 62322</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>68711; 85773</t>
+          <t>70068; 86702</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>91880; 111581</t>
+          <t>90522; 112316</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>92979; 111654</t>
+          <t>93876; 111734</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>131442; 153934</t>
+          <t>128439; 146337</t>
         </is>
       </c>
     </row>
@@ -2831,42 +2831,42 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>44</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>46</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
           <t>36</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>28</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="I19" s="2" t="inlineStr">
         <is>
           <t>35</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr">
+      <c r="J19" s="2" t="inlineStr">
         <is>
           <t>52</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>44</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>31</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>46</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
@@ -2899,42 +2899,42 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>27867</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>31341</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>22753</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>37765</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
           <t>23970</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="H20" s="2" t="inlineStr">
         <is>
           <t>20305</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="I20" s="2" t="inlineStr">
         <is>
           <t>24916</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>38130</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>27867</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>31341</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>22753</t>
-        </is>
-      </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>38081</t>
+          <t>40343</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>76211</t>
+          <t>78108</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>19001; 28827</t>
+          <t>23853; 31172</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>16603; 23075</t>
+          <t>26667; 34301</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20409; 28189</t>
+          <t>18040; 27066</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>32757; 41409</t>
+          <t>32376; 41783</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>23128; 31117</t>
+          <t>19098; 28849</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>27058; 34353</t>
+          <t>16823; 23219</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>18005; 26962</t>
+          <t>20229; 28408</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>32273; 41476</t>
+          <t>35110; 43794</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>44703; 57631</t>
+          <t>45274; 58170</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>46159; 56118</t>
+          <t>46053; 56164</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>41113; 52849</t>
+          <t>41276; 53503</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>68276; 81329</t>
+          <t>69533; 83558</t>
         </is>
       </c>
     </row>
@@ -3039,42 +3039,42 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>375</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>368</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>367</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>466</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
           <t>327</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="H22" s="2" t="inlineStr">
         <is>
           <t>345</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="I22" s="2" t="inlineStr">
         <is>
           <t>361</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr">
+      <c r="J22" s="2" t="inlineStr">
         <is>
           <t>453</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>375</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>368</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>367</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>466</t>
         </is>
       </c>
       <c r="K22" s="2" t="inlineStr">
@@ -3107,42 +3107,42 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>248367</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>257230</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>266253</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>375521</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
           <t>217689</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t>243284</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="I23" s="2" t="inlineStr">
         <is>
           <t>250816</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>315046</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>248367</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>257230</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>266253</t>
-        </is>
-      </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>393920</t>
+          <t>319306</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>708966</t>
+          <t>694826</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>202719; 231756</t>
+          <t>234586; 261934</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>228337; 255335</t>
+          <t>242858; 269783</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>235980; 262704</t>
+          <t>252266; 278550</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>299245; 328047</t>
+          <t>358571; 390184</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>234759; 262521</t>
+          <t>204210; 231546</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>243964; 270248</t>
+          <t>228148; 255694</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>253404; 279682</t>
+          <t>236545; 263626</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>376745; 410032</t>
+          <t>303183; 330822</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>447790; 484070</t>
+          <t>448311; 485741</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>479693; 518529</t>
+          <t>480724; 518535</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>496942; 537207</t>
+          <t>499916; 536808</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>686202; 729860</t>
+          <t>672881; 717203</t>
         </is>
       </c>
     </row>
